--- a/excel-files/MANDALUYONG/FILEMON P. JAVIER ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/MANDALUYONG/FILEMON P. JAVIER ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29728"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="593" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12A4267D-468E-4787-B5D3-267DDD5D69E8}"/>
+  <xr:revisionPtr revIDLastSave="620" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DB33DF0-3793-4E14-AFA5-C128EF187EAF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="94">
   <si>
     <t>Grade Level</t>
   </si>
@@ -95,6 +95,9 @@
   </si>
   <si>
     <t>Araling Panlipunan</t>
+  </si>
+  <si>
+    <t>qqqqqqqqqqqqqqqqqqqqqqqqqqqq</t>
   </si>
   <si>
     <t>PE and Health</t>
@@ -3501,7 +3504,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -3545,7 +3548,9 @@
       <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1"/>
+      <c r="C2" s="1">
+        <v>77</v>
+      </c>
       <c r="D2" s="1">
         <v>103</v>
       </c>
@@ -3560,7 +3565,7 @@
       </c>
       <c r="H2" s="4">
         <f>IF((D2-C2)&lt;0,0,D2-C2)</f>
-        <v>103</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="29.25" customHeight="1">
@@ -3570,7 +3575,9 @@
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1"/>
+      <c r="C3" s="1">
+        <v>77</v>
+      </c>
       <c r="D3" s="1">
         <v>103</v>
       </c>
@@ -3585,7 +3592,7 @@
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H6" si="0">IF((D3-C3)&lt;0,0,D3-C3)</f>
-        <v>103</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21" customHeight="1">
@@ -3595,7 +3602,9 @@
       <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1"/>
+      <c r="C4" s="1">
+        <v>77</v>
+      </c>
       <c r="D4" s="1">
         <v>103</v>
       </c>
@@ -3610,7 +3619,7 @@
       </c>
       <c r="H4" s="4">
         <f>IF((D4-C4)&lt;0,0,D4-C4)</f>
-        <v>103</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25.5" customHeight="1">
@@ -3620,7 +3629,9 @@
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="1"/>
+      <c r="C5" s="1">
+        <v>77</v>
+      </c>
       <c r="D5" s="1">
         <v>103</v>
       </c>
@@ -3635,7 +3646,7 @@
       </c>
       <c r="H5" s="4">
         <f>IF((D5-C5)&lt;0,0,D5-C5)</f>
-        <v>103</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="19.5">
@@ -3645,7 +3656,9 @@
       <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="C6" s="1">
+        <v>77</v>
+      </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="5"/>
@@ -3669,13 +3682,15 @@
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="1"/>
+      <c r="C8" s="1">
+        <v>63</v>
+      </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="5"/>
       <c r="G8" s="3">
         <f>IF((C8-D8)&lt;0,0,C8-D8)</f>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H8" s="4">
         <f>IF((D8-C8)&lt;0,0,D8-C8)</f>
@@ -3689,7 +3704,9 @@
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="1"/>
+      <c r="C9" s="1">
+        <v>63</v>
+      </c>
       <c r="D9" s="1">
         <v>58</v>
       </c>
@@ -3704,7 +3721,7 @@
       </c>
       <c r="H9" s="4">
         <f>IF((D9-C9)&lt;0,0,D9-C9)</f>
-        <v>58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="28.5" customHeight="1">
@@ -3714,13 +3731,15 @@
       <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="1"/>
+      <c r="C10" s="1">
+        <v>63</v>
+      </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="5"/>
       <c r="G10" s="3">
         <f>IF((C10-D10)&lt;0,0,C10-D10)</f>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H10" s="4">
         <f>IF((D10-C10)&lt;0,0,D10-C10)</f>
@@ -3734,33 +3753,37 @@
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="1"/>
+      <c r="C11" s="1">
+        <v>63</v>
+      </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="5"/>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="19.149999999999999">
+    <row r="12" spans="1:8" ht="19.5">
       <c r="A12" s="1">
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="1">
+        <v>63</v>
+      </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="5"/>
       <c r="G12" s="3">
         <f>IF((C12-D12)&lt;0,0,C12-D12)</f>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H12" s="4">
         <f>IF((D12-C12)&lt;0,0,D12-C12)</f>
@@ -3779,13 +3802,15 @@
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="1"/>
+      <c r="C14" s="1">
+        <v>58</v>
+      </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="5"/>
       <c r="G14" s="3">
         <f t="shared" ref="G14:G19" si="1">IF((C14-D14)&lt;0,0,C14-D14)</f>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" ref="H14:H20" si="2">IF((D14-C14)&lt;0,0,D14-C14)</f>
@@ -3799,13 +3824,15 @@
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="1"/>
+      <c r="C15" s="1">
+        <v>58</v>
+      </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="5"/>
       <c r="G15" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="2"/>
@@ -3819,67 +3846,75 @@
       <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="1"/>
+      <c r="C16" s="1">
+        <v>58</v>
+      </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="5"/>
       <c r="G16" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="H16" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="23.25" customHeight="1">
+    <row r="17" spans="1:10" ht="23.25" customHeight="1">
       <c r="A17" s="1">
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="1"/>
+      <c r="C17" s="1">
+        <v>58</v>
+      </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="5"/>
       <c r="G17" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="H17" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="21" customHeight="1">
+    <row r="18" spans="1:10" ht="21" customHeight="1">
       <c r="A18" s="1">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="1"/>
+      <c r="C18" s="1">
+        <v>58</v>
+      </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="5"/>
       <c r="G18" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.5">
+    <row r="19" spans="1:10" ht="19.5">
       <c r="A19" s="1">
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="1"/>
+      <c r="C19" s="1">
+        <v>58</v>
+      </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="5"/>
@@ -3891,7 +3926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15">
+    <row r="20" spans="1:10" ht="15">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -3901,34 +3936,38 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="28.5" customHeight="1">
+    <row r="21" spans="1:10" ht="28.5" customHeight="1">
       <c r="A21" s="1">
         <v>4</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="1"/>
+      <c r="C21" s="1">
+        <v>76</v>
+      </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="5"/>
       <c r="G21" s="3">
         <f t="shared" ref="G21:G29" si="3">IF((C21-D21)&lt;0,0,C21-D21)</f>
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" ref="H21:H29" si="4">IF((D21-C21)&lt;0,0,D21-C21)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="24" customHeight="1">
+    <row r="22" spans="1:10" ht="24" customHeight="1">
       <c r="A22" s="1">
         <v>4</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="1"/>
+      <c r="C22" s="1">
+        <v>76</v>
+      </c>
       <c r="D22" s="1">
         <v>73</v>
       </c>
@@ -3943,17 +3982,19 @@
       </c>
       <c r="H22" s="4">
         <f t="shared" si="4"/>
-        <v>73</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="19.5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="19.5">
       <c r="A23" s="1">
         <v>4</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="1"/>
+      <c r="C23" s="1">
+        <v>76</v>
+      </c>
       <c r="D23" s="1">
         <v>73</v>
       </c>
@@ -3965,21 +4006,23 @@
       </c>
       <c r="G23" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="4"/>
-        <v>73</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="27" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="27" customHeight="1">
       <c r="A24" s="1">
         <v>4</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="1"/>
+      <c r="C24" s="1">
+        <v>76</v>
+      </c>
       <c r="D24" s="1">
         <v>73</v>
       </c>
@@ -3994,17 +4037,19 @@
       </c>
       <c r="H24" s="4">
         <f t="shared" si="4"/>
-        <v>73</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="33.75" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="33.75" customHeight="1">
       <c r="A25" s="1">
         <v>4</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="1"/>
+      <c r="C25" s="1">
+        <v>76</v>
+      </c>
       <c r="D25" s="1">
         <v>73</v>
       </c>
@@ -4016,21 +4061,26 @@
       </c>
       <c r="G25" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="4"/>
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="33.75" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="J25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="33.75" customHeight="1">
       <c r="A26" s="1">
         <v>4</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="1"/>
+      <c r="C26" s="1">
+        <v>76</v>
+      </c>
       <c r="D26" s="1">
         <v>73</v>
       </c>
@@ -4042,21 +4092,23 @@
       </c>
       <c r="G26" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H26" s="4">
         <f t="shared" si="4"/>
-        <v>73</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="33.75" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="33.75" customHeight="1">
       <c r="A27" s="1">
         <v>4</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="C27" s="1">
+        <v>76</v>
+      </c>
       <c r="D27" s="1">
         <v>73</v>
       </c>
@@ -4068,54 +4120,58 @@
       </c>
       <c r="G27" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H27" s="4">
         <f t="shared" si="4"/>
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="27.75" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="27.75" customHeight="1">
       <c r="A28" s="1">
         <v>4</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="C28" s="1">
+        <v>76</v>
+      </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="5"/>
       <c r="G28" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="27.75" customHeight="1">
+    <row r="29" spans="1:10" ht="27.75" customHeight="1">
       <c r="A29" s="1">
         <v>4</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="C29" s="1">
+        <v>76</v>
+      </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="5"/>
       <c r="G29" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="27.75" customHeight="1">
+    <row r="30" spans="1:10" ht="27.75" customHeight="1">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
@@ -4125,40 +4181,44 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" ht="27.75" customHeight="1">
+    <row r="31" spans="1:10" ht="27.75" customHeight="1">
       <c r="A31" s="1">
         <v>5</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="1"/>
+      <c r="C31" s="1">
+        <v>64</v>
+      </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="5"/>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="5">IF((C31-D31)&lt;0,0,C31-D31)</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:I39" si="6">IF((D31-C31)&lt;0,0,D31-C31)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="27.75" customHeight="1">
+    <row r="32" spans="1:10" ht="27.75" customHeight="1">
       <c r="A32" s="1">
         <v>5</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C32" s="1"/>
+      <c r="C32" s="1">
+        <v>64</v>
+      </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="5"/>
       <c r="G32" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="6"/>
@@ -4172,13 +4232,15 @@
       <c r="B33" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="1"/>
+      <c r="C33" s="1">
+        <v>64</v>
+      </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="5"/>
       <c r="G33" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="6"/>
@@ -4192,13 +4254,15 @@
       <c r="B34" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C34" s="1"/>
+      <c r="C34" s="1">
+        <v>64</v>
+      </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="5"/>
       <c r="G34" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="6"/>
@@ -4212,7 +4276,9 @@
       <c r="B35" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="1"/>
+      <c r="C35" s="1">
+        <v>64</v>
+      </c>
       <c r="D35" s="1">
         <v>70</v>
       </c>
@@ -4228,7 +4294,7 @@
       </c>
       <c r="H35" s="4">
         <f t="shared" si="6"/>
-        <v>70</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="27.75" customHeight="1">
@@ -4238,13 +4304,15 @@
       <c r="B36" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="1"/>
+      <c r="C36" s="1">
+        <v>64</v>
+      </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="5"/>
       <c r="G36" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="6"/>
@@ -4256,15 +4324,17 @@
         <v>5</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C37" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="C37" s="1">
+        <v>64</v>
+      </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="5"/>
       <c r="G37" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="6"/>
@@ -4276,15 +4346,17 @@
         <v>5</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="C38" s="1">
+        <v>64</v>
+      </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="5"/>
       <c r="G38" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="6"/>
@@ -4296,15 +4368,17 @@
         <v>5</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C39" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="C39" s="1">
+        <v>64</v>
+      </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="5"/>
       <c r="G39" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="6"/>
@@ -4328,13 +4402,15 @@
       <c r="B41" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C41" s="1"/>
+      <c r="C41" s="1">
+        <v>65</v>
+      </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="5"/>
       <c r="G41" s="3">
         <f t="shared" ref="G41:G49" si="7">IF((C41-D41)&lt;0,0,C41-D41)</f>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H41" s="4">
         <f t="shared" ref="H41:H49" si="8">IF((D41-C41)&lt;0,0,D41-C41)</f>
@@ -4348,13 +4424,15 @@
       <c r="B42" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C42" s="1"/>
+      <c r="C42" s="1">
+        <v>65</v>
+      </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="5"/>
       <c r="G42" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H42" s="4">
         <f t="shared" si="8"/>
@@ -4368,13 +4446,15 @@
       <c r="B43" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C43" s="1"/>
+      <c r="C43" s="1">
+        <v>65</v>
+      </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="5"/>
       <c r="G43" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H43" s="4">
         <f t="shared" si="8"/>
@@ -4388,13 +4468,15 @@
       <c r="B44" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C44" s="1"/>
+      <c r="C44" s="1">
+        <v>65</v>
+      </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="5"/>
       <c r="G44" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H44" s="4">
         <f t="shared" si="8"/>
@@ -4408,13 +4490,15 @@
       <c r="B45" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C45" s="1"/>
+      <c r="C45" s="1">
+        <v>65</v>
+      </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="5"/>
       <c r="G45" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H45" s="4">
         <f t="shared" si="8"/>
@@ -4428,7 +4512,9 @@
       <c r="B46" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C46" s="1"/>
+      <c r="C46" s="1">
+        <v>65</v>
+      </c>
       <c r="D46" s="1">
         <v>78</v>
       </c>
@@ -4444,7 +4530,7 @@
       </c>
       <c r="H46" s="4">
         <f t="shared" si="8"/>
-        <v>78</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="27.75" customHeight="1">
@@ -4452,15 +4538,17 @@
         <v>6</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C47" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="C47" s="1">
+        <v>65</v>
+      </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="5"/>
       <c r="G47" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H47" s="4">
         <f t="shared" si="8"/>
@@ -4472,15 +4560,17 @@
         <v>6</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="C48" s="1">
+        <v>65</v>
+      </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="5"/>
       <c r="G48" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H48" s="4">
         <f t="shared" si="8"/>
@@ -4492,15 +4582,17 @@
         <v>6</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C49" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="C49" s="1">
+        <v>65</v>
+      </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="5"/>
       <c r="G49" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H49" s="4">
         <f t="shared" si="8"/>
@@ -4582,7 +4674,7 @@
         <v>7</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C54" s="10"/>
       <c r="D54" s="10"/>
@@ -4642,7 +4734,7 @@
         <v>7</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="10"/>
@@ -4662,7 +4754,7 @@
         <v>7</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C58" s="10"/>
       <c r="D58" s="10"/>
@@ -4682,7 +4774,7 @@
         <v>7</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="10"/>
@@ -4772,7 +4864,7 @@
         <v>8</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C64" s="10"/>
       <c r="D64" s="10"/>
@@ -4792,7 +4884,7 @@
         <v>8</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
@@ -4832,7 +4924,7 @@
         <v>8</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="10"/>
@@ -4852,7 +4944,7 @@
         <v>8</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="10"/>
@@ -4872,7 +4964,7 @@
         <v>8</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="10"/>
@@ -4962,7 +5054,7 @@
         <v>9</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="10"/>
@@ -4982,7 +5074,7 @@
         <v>9</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
@@ -5022,7 +5114,7 @@
         <v>9</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="10"/>
@@ -5042,7 +5134,7 @@
         <v>9</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="10"/>
@@ -5062,7 +5154,7 @@
         <v>9</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="10"/>
@@ -5152,7 +5244,7 @@
         <v>10</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="10"/>
@@ -5172,7 +5264,7 @@
         <v>10</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="10"/>
@@ -5212,7 +5304,7 @@
         <v>10</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
@@ -5232,7 +5324,7 @@
         <v>10</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="10"/>
@@ -5252,7 +5344,7 @@
         <v>10</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="10"/>
@@ -5279,10 +5371,10 @@
     </row>
     <row r="91" spans="1:8" ht="39.75" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
@@ -5299,10 +5391,10 @@
     </row>
     <row r="92" spans="1:8" ht="27.75" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
@@ -5319,10 +5411,10 @@
     </row>
     <row r="93" spans="1:8" ht="27.75" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
@@ -5339,10 +5431,10 @@
     </row>
     <row r="94" spans="1:8" ht="27.75" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
@@ -5359,10 +5451,10 @@
     </row>
     <row r="95" spans="1:8" ht="40.5" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
@@ -5379,10 +5471,10 @@
     </row>
     <row r="96" spans="1:8" ht="38.25" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
@@ -5399,10 +5491,10 @@
     </row>
     <row r="97" spans="1:8" ht="27.75" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
@@ -5419,10 +5511,10 @@
     </row>
     <row r="98" spans="1:8" ht="47.25" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
@@ -5444,8 +5536,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5464,7 +5556,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5482,7 +5574,7 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="D1" s="44" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E1" s="44"/>
       <c r="F1" s="44"/>
@@ -5490,7 +5582,7 @@
       <c r="H1" s="44"/>
       <c r="I1" s="44"/>
       <c r="J1" s="45" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K1" s="45"/>
       <c r="L1" s="45"/>
@@ -5498,7 +5590,7 @@
       <c r="N1" s="45"/>
       <c r="O1" s="45"/>
       <c r="P1" s="46" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q1" s="46"/>
       <c r="R1" s="46"/>
@@ -5506,7 +5598,7 @@
       <c r="T1" s="46"/>
       <c r="U1" s="46"/>
       <c r="V1" s="47" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W1" s="47"/>
       <c r="X1" s="47"/>
@@ -5525,81 +5617,81 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M2" s="40" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N2" s="40" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O2" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q2" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="R2" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U2" s="24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V2" s="26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Y2" s="41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Z2" s="41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AA2" s="26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="30.6" customHeight="1">
       <c r="A3" s="39" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="32">
@@ -5613,7 +5705,7 @@
         <v>270</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3" s="34" t="s">
         <v>9</v>
@@ -6262,7 +6354,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C12" s="1">
         <v>79</v>
@@ -6885,7 +6977,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C21" s="1">
         <v>65</v>
@@ -7586,7 +7678,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C31" s="1">
         <v>58</v>
@@ -8133,7 +8225,7 @@
         <v>4</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C39" s="1">
         <v>76</v>
@@ -8210,7 +8302,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C40" s="1">
         <v>76</v>
@@ -8287,7 +8379,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C41" s="1">
         <v>76</v>
@@ -8864,7 +8956,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C49" s="1">
         <v>63</v>
@@ -8941,7 +9033,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C50" s="1">
         <v>63</v>
@@ -9018,7 +9110,7 @@
         <v>5</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C51" s="1">
         <v>63</v>
@@ -9535,7 +9627,7 @@
         <v>6</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C59" s="1">
         <v>65</v>
@@ -9606,7 +9698,7 @@
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C60" s="1">
         <v>65</v>
@@ -9677,7 +9769,7 @@
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C61" s="1">
         <v>65</v>
@@ -9969,7 +10061,7 @@
         <v>7</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C66" s="10"/>
       <c r="D66" s="12">
@@ -10176,7 +10268,7 @@
         <v>7</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="12">
@@ -10245,7 +10337,7 @@
         <v>7</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="12">
@@ -10314,7 +10406,7 @@
         <v>7</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="12">
@@ -10604,7 +10696,7 @@
         <v>8</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C76" s="10"/>
       <c r="D76" s="12">
@@ -10673,7 +10765,7 @@
         <v>8</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="12">
@@ -10811,7 +10903,7 @@
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="12">
@@ -10880,7 +10972,7 @@
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="12">
@@ -10949,7 +11041,7 @@
         <v>8</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="12">
@@ -11239,7 +11331,7 @@
         <v>9</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="12">
@@ -11308,7 +11400,7 @@
         <v>9</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="12">
@@ -11446,7 +11538,7 @@
         <v>9</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="12">
@@ -11515,7 +11607,7 @@
         <v>9</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C90" s="10"/>
       <c r="D90" s="12">
@@ -11584,7 +11676,7 @@
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="12">
@@ -11874,7 +11966,7 @@
         <v>10</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C96" s="10"/>
       <c r="D96" s="12">
@@ -11943,7 +12035,7 @@
         <v>10</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="12">
@@ -12081,7 +12173,7 @@
         <v>10</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="12">
@@ -12150,7 +12242,7 @@
         <v>10</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="12">
@@ -12219,7 +12311,7 @@
         <v>10</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="12">
@@ -12299,10 +12391,10 @@
     </row>
     <row r="103" spans="1:27" ht="38.450000000000003">
       <c r="A103" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="5">
@@ -12368,10 +12460,10 @@
     </row>
     <row r="104" spans="1:27" ht="19.149999999999999">
       <c r="A104" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="5">
@@ -12437,10 +12529,10 @@
     </row>
     <row r="105" spans="1:27" ht="19.149999999999999">
       <c r="A105" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="5">
@@ -12506,10 +12598,10 @@
     </row>
     <row r="106" spans="1:27" ht="19.149999999999999">
       <c r="A106" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="5">
@@ -12575,10 +12667,10 @@
     </row>
     <row r="107" spans="1:27" ht="38.450000000000003">
       <c r="A107" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="5">
@@ -12644,10 +12736,10 @@
     </row>
     <row r="108" spans="1:27" ht="19.149999999999999">
       <c r="A108" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="5">
@@ -12713,10 +12805,10 @@
     </row>
     <row r="109" spans="1:27" ht="38.450000000000003">
       <c r="A109" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="5">
@@ -12782,10 +12874,10 @@
     </row>
     <row r="110" spans="1:27" ht="38.450000000000003">
       <c r="A110" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="5">
@@ -13847,186 +13939,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -14046,8 +13958,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -14069,7 +13981,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -14088,7 +14000,7 @@
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
       <c r="D1" s="44" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E1" s="44"/>
       <c r="F1" s="44"/>
@@ -14096,7 +14008,7 @@
       <c r="H1" s="44"/>
       <c r="I1" s="44"/>
       <c r="J1" s="45" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K1" s="45"/>
       <c r="L1" s="45"/>
@@ -14104,7 +14016,7 @@
       <c r="N1" s="45"/>
       <c r="O1" s="45"/>
       <c r="P1" s="46" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q1" s="46"/>
       <c r="R1" s="46"/>
@@ -14112,7 +14024,7 @@
       <c r="T1" s="46"/>
       <c r="U1" s="46"/>
       <c r="V1" s="47" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W1" s="47"/>
       <c r="X1" s="47"/>
@@ -14131,76 +14043,76 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M2" s="40" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N2" s="40" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O2" s="22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q2" s="24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R2" s="25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U2" s="24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V2" s="26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Y2" s="41" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Z2" s="41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AA2" s="26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="36.75" customHeight="1">
@@ -14705,7 +14617,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C10" s="1">
         <v>79</v>
@@ -15292,7 +15204,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C19" s="1">
         <v>65</v>
@@ -15962,7 +15874,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C29" s="1">
         <v>58</v>
@@ -16460,7 +16372,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C37" s="5">
         <v>76</v>
@@ -16531,7 +16443,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C38" s="1">
         <v>76</v>
@@ -16602,7 +16514,7 @@
         <v>4</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C39" s="1">
         <v>76</v>
@@ -16673,7 +16585,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C40" s="5">
         <v>76</v>
@@ -16744,7 +16656,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C41" s="1">
         <v>76</v>
@@ -17242,7 +17154,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C49" s="5">
         <v>63</v>
@@ -17313,7 +17225,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C50" s="1">
         <v>63</v>
@@ -17384,7 +17296,7 @@
         <v>5</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C51" s="1">
         <v>63</v>
@@ -17455,7 +17367,7 @@
         <v>5</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C52" s="5">
         <v>63</v>
@@ -17526,7 +17438,7 @@
         <v>5</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C53" s="1">
         <v>63</v>
@@ -18122,7 +18034,7 @@
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C61" s="5">
         <v>65</v>
@@ -18199,7 +18111,7 @@
         <v>6</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C62" s="1">
         <v>65</v>
@@ -18282,7 +18194,7 @@
         <v>6</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C63" s="1">
         <v>65</v>
@@ -18353,7 +18265,7 @@
         <v>6</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C64" s="5">
         <v>65</v>
@@ -18436,7 +18348,7 @@
         <v>6</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C65" s="1">
         <v>65</v>
@@ -18727,7 +18639,7 @@
         <v>7</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="12">
@@ -18934,7 +18846,7 @@
         <v>7</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C73" s="12"/>
       <c r="D73" s="12">
@@ -19003,7 +18915,7 @@
         <v>7</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -19072,7 +18984,7 @@
         <v>7</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="12">
@@ -19141,7 +19053,7 @@
         <v>7</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C76" s="12"/>
       <c r="D76" s="12">
@@ -19210,7 +19122,7 @@
         <v>7</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="12">
@@ -19487,7 +19399,7 @@
         <v>8</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="12">
@@ -19556,7 +19468,7 @@
         <v>8</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="12">
@@ -19694,7 +19606,7 @@
         <v>8</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C85" s="12"/>
       <c r="D85" s="12">
@@ -19763,7 +19675,7 @@
         <v>8</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="12">
@@ -19832,7 +19744,7 @@
         <v>8</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="12">
@@ -19901,7 +19813,7 @@
         <v>8</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C88" s="12"/>
       <c r="D88" s="12">
@@ -19970,7 +19882,7 @@
         <v>8</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="12">
@@ -20247,7 +20159,7 @@
         <v>9</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="12">
@@ -20316,7 +20228,7 @@
         <v>9</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="12">
@@ -20454,7 +20366,7 @@
         <v>9</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="12">
@@ -20523,7 +20435,7 @@
         <v>9</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -20592,7 +20504,7 @@
         <v>9</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="12">
@@ -20661,7 +20573,7 @@
         <v>9</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="12">
@@ -20730,7 +20642,7 @@
         <v>9</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="12">
@@ -21007,7 +20919,7 @@
         <v>10</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C106" s="10"/>
       <c r="D106" s="12">
@@ -21076,7 +20988,7 @@
         <v>10</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="12">
@@ -21214,7 +21126,7 @@
         <v>10</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="12">
@@ -21283,7 +21195,7 @@
         <v>10</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C110" s="10"/>
       <c r="D110" s="12">
@@ -21352,7 +21264,7 @@
         <v>10</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="12">
@@ -21421,7 +21333,7 @@
         <v>10</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C112" s="10"/>
       <c r="D112" s="12">
@@ -21490,7 +21402,7 @@
         <v>10</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="12">
@@ -21557,10 +21469,10 @@
     <row r="114" spans="1:28" s="7" customFormat="1"/>
     <row r="115" spans="1:28" ht="38.450000000000003">
       <c r="A115" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="5">
@@ -21626,10 +21538,10 @@
     </row>
     <row r="116" spans="1:28" ht="19.149999999999999">
       <c r="A116" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="5">
@@ -21695,10 +21607,10 @@
     </row>
     <row r="117" spans="1:28" ht="19.149999999999999">
       <c r="A117" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="5">
@@ -21764,10 +21676,10 @@
     </row>
     <row r="118" spans="1:28" ht="19.149999999999999">
       <c r="A118" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="5">
@@ -21833,10 +21745,10 @@
     </row>
     <row r="119" spans="1:28" ht="38.450000000000003">
       <c r="A119" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="5">
@@ -21902,10 +21814,10 @@
     </row>
     <row r="120" spans="1:28" ht="19.149999999999999">
       <c r="A120" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="5">
@@ -21971,10 +21883,10 @@
     </row>
     <row r="121" spans="1:28" ht="38.450000000000003">
       <c r="A121" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="5">
@@ -22040,10 +21952,10 @@
     </row>
     <row r="122" spans="1:28" ht="38.450000000000003">
       <c r="A122" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="5">
@@ -22618,186 +22530,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22815,8 +22547,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
